--- a/practice-files/day19-SQL入门-示例数据.xlsx
+++ b/practice-files/day19-SQL入门-示例数据.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="示例数据-world风格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="思考题" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,22 @@
       <name val="Consolas"/>
       <color rgb="004472C4"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -96,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +122,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -972,4 +994,56 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>思考题1: 在本文件的模拟world表上，写出"查询亚洲国家名字和人口"的SQL。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" outlineLevel="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>💡 答案: SELECT name, population FROM [表] WHERE continent = 'Asia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>思考题2: "WHERE population &gt; 100000000 AND area &gt; 1000000"会返回哪些国家？</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>💡 答案: China、India、United States、Indonesia、Brazil、Russia、Mexico、Egypt 共8个。注意：Japan、Nigeria人口达标但面积不够；Vietnam人口差一点不到1亿。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day19-SQL入门-示例数据.xlsx
+++ b/practice-files/day19-SQL入门-示例数据.xlsx
@@ -1011,7 +1011,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>💡 答案: SELECT name, population FROM [表] WHERE continent = 'Asia'</t>
+          <t>答案: SELECT name, population FROM [表] WHERE continent = 'Asia'</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="7" hidden="1" outlineLevel="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>💡 答案: China、India、United States、Indonesia、Brazil、Russia、Mexico、Egypt 共8个。注意：Japan、Nigeria人口达标但面积不够；Vietnam人口差一点不到1亿。</t>
+          <t>答案: China、India、United States、Indonesia、Brazil、Russia、Mexico、Egypt 共8个。注意：Japan、Nigeria人口达标但面积不够；Vietnam人口差一点不到1亿。</t>
         </is>
       </c>
     </row>
